--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_128_R13.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_128_R13.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. GRAHAM</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2285</v>
+        <v>5.8619</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1281</v>
+        <v>5.1307</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1004</v>
+        <v>0.7312</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8788</v>
+        <v>3.9896</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7299</v>
+        <v>-0.2197</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1489</v>
+        <v>4.2093</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8107</v>
+        <v>4.1251</v>
       </c>
       <c r="K2" t="n">
-        <v>0.605</v>
+        <v>-0.1443</v>
       </c>
       <c r="L2" t="n">
-        <v>4.2057</v>
+        <v>4.2694</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.1355</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1249</v>
+        <v>-0.0755</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0568</v>
+        <v>-0.06</v>
       </c>
       <c r="P2" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1177</v>
+        <v>0.0167</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5228</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6405</v>
+        <v>0.0833</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>D. GRAHAM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1726</v>
+        <v>5.2463</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0128</v>
+        <v>3.482</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1598</v>
+        <v>1.7643</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9896</v>
+        <v>4.8788</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2197</v>
+        <v>0.7299</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2093</v>
+        <v>4.1489</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1251</v>
+        <v>4.8107</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1443</v>
+        <v>0.605</v>
       </c>
       <c r="L3" t="n">
-        <v>4.2694</v>
+        <v>4.2057</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1355</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0755</v>
+        <v>0.1249</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.06</v>
+        <v>-0.0568</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6726</v>
+        <v>0.1355</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1845</v>
+        <v>-0.1689</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4881</v>
+        <v>0.3044</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0486</v>
+        <v>2.9366</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7134</v>
+        <v>3.8194</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3352</v>
+        <v>-0.8828</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7299</v>
+        <v>0.3053</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9376</v>
+        <v>0.7705</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2076</v>
+        <v>-0.4651</v>
       </c>
       <c r="J4" t="n">
-        <v>1.257</v>
+        <v>2.3852</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3256</v>
+        <v>1.3717</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5826</v>
+        <v>1.0136</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9869</v>
+        <v>-2.0799</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.612</v>
+        <v>-0.6012</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.375</v>
+        <v>-1.4787</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>2.7834</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.7112</v>
+        <v>2.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1212</v>
+        <v>-0.5465</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4381</v>
+        <v>0.362</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6831</v>
+        <v>-0.9085</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4254</v>
+        <v>0.3943</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4975</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BUTLER</t>
+          <t>D. MOTIEJUNAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7782</v>
+        <v>2.1725</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4626</v>
+        <v>2.014</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3156</v>
+        <v>0.1585</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1748</v>
+        <v>-0.4816</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5127</v>
+        <v>-0.3913</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3379</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1392</v>
+        <v>0.8693</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4804</v>
+        <v>-0.1478</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3412</v>
+        <v>1.0171</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0356</v>
+        <v>-1.3509</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0323</v>
+        <v>-0.2435</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0033</v>
+        <v>-1.1074</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1644</v>
+        <v>-0.114</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7616</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4028</v>
+        <v>-0.8101</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7886</v>
+        <v>1.6083</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MOTIEJUNAS</t>
+          <t>J. BUTLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.377</v>
+        <v>1.6488</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2184</v>
+        <v>-0.8348</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1585</v>
+        <v>2.4836</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4816</v>
+        <v>-0.1748</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3913</v>
+        <v>-0.5127</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09030000000000001</v>
+        <v>0.3379</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8693</v>
+        <v>-0.1392</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1478</v>
+        <v>-0.4804</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0171</v>
+        <v>0.3412</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3509</v>
+        <v>-0.0356</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2435</v>
+        <v>-0.0323</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1074</v>
+        <v>-0.0033</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3195</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0905</v>
+        <v>1.035</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9006</v>
+        <v>0.4641</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8101</v>
+        <v>0.5709</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6083</v>
+        <v>0.7886</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3154</v>
+        <v>1.3456</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1983</v>
+        <v>0.4473</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8828</v>
+        <v>0.8983</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3053</v>
+        <v>-0.7299</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7705</v>
+        <v>-0.9376</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4651</v>
+        <v>0.2076</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3852</v>
+        <v>1.257</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3717</v>
+        <v>-0.3256</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0136</v>
+        <v>1.5826</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0799</v>
+        <v>-1.9869</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6012</v>
+        <v>-0.612</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4787</v>
+        <v>-1.375</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7834</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7834</v>
+        <v>3.7112</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1677</v>
+        <v>1.4183</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2592</v>
+        <v>1.172</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9085</v>
+        <v>0.2462</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3943</v>
+        <v>0.4254</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>1.4975</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7395</v>
+        <v>0.1686</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6575</v>
+        <v>0.6055</v>
       </c>
       <c r="F8" t="n">
-        <v>1.918</v>
+        <v>-0.4369</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8811</v>
+        <v>0.5327</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0793</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9603</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3775</v>
+        <v>2.7164</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1547</v>
+        <v>1.385</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5322</v>
+        <v>1.3314</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5036</v>
+        <v>-2.1837</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0755</v>
+        <v>-0.7584</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4281</v>
+        <v>-1.4252</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6445</v>
+        <v>-0.06</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1202</v>
+        <v>0.2087</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4758</v>
+        <v>-0.2686</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9923</v>
+        <v>0.1437</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7234</v>
+        <v>-1.8751</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2689</v>
+        <v>2.0188</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5327</v>
+        <v>-0.8811</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.0793</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.9603</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7164</v>
+        <v>-0.3775</v>
       </c>
       <c r="K9" t="n">
-        <v>1.385</v>
+        <v>0.1547</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3314</v>
+        <v>-0.5322</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1837</v>
+        <v>-0.5036</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7584</v>
+        <v>-0.0755</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4252</v>
+        <v>-0.4281</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2208</v>
+        <v>0.2388</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1202</v>
+        <v>-0.3378</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1006</v>
+        <v>0.5766</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0405</v>
+        <v>-2.0069</v>
       </c>
       <c r="E10" t="n">
         <v>-0.07580000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9647</v>
+        <v>-1.9311</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6841</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2842</v>
+        <v>-0.2506</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3621</v>
+        <v>-2.9843</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6243</v>
+        <v>-2.3138</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7377</v>
+        <v>-0.6705</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1804</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7178</v>
+        <v>-0.34</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2636</v>
+        <v>0.5742</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-0.9142</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.7859</v>
+        <v>14.5328</v>
       </c>
       <c r="E12" t="n">
-        <v>9.652600000000001</v>
+        <v>10.3994</v>
       </c>
       <c r="F12" t="n">
         <v>4.1334</v>
       </c>
       <c r="G12" t="n">
-        <v>4.574499999999999</v>
+        <v>4.5745</v>
       </c>
       <c r="H12" t="n">
         <v>0.1078</v>
@@ -1390,13 +1390,13 @@
         <v>19.7159</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7862000000000007</v>
+        <v>1.533199999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.0076</v>
+        <v>2.7544</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2214</v>
+        <v>-1.2213</v>
       </c>
       <c r="V12" t="n">
         <v>1.4665</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8944</v>
+        <v>1.732</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5102</v>
+        <v>2.4486</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6158</v>
+        <v>-0.7166</v>
       </c>
       <c r="G13" t="n">
         <v>0.8018</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0925</v>
+        <v>-0.0698</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6201</v>
+        <v>0.5586</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5276</v>
+        <v>-0.6284</v>
       </c>
       <c r="V13" t="n">
         <v>0.5361</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8376</v>
+        <v>1.5865</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9688</v>
+        <v>3.3227</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1312</v>
+        <v>-1.7361</v>
       </c>
       <c r="G14" t="n">
         <v>2.4072</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1599</v>
+        <v>-0.411</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4753</v>
+        <v>-0.1215</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3154</v>
+        <v>-0.2895</v>
       </c>
       <c r="V14" t="n">
         <v>1.214</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0738</v>
+        <v>-0.5012</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2631</v>
+        <v>0.7349</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3369</v>
+        <v>-1.2361</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7495000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4635</v>
+        <v>0.1092</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5895</v>
+        <v>-0.1177</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1261</v>
+        <v>0.2269</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7886</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2421</v>
+        <v>-1.2513</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.484</v>
+        <v>-0.3368</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7581</v>
+        <v>-0.9145</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7094</v>
+        <v>1.597</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1332</v>
+        <v>0.2185</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5762</v>
+        <v>1.3785</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3692</v>
+        <v>2.8905</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.215</v>
+        <v>0.6624</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1543</v>
+        <v>2.2281</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3401</v>
+        <v>-1.2936</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0818</v>
+        <v>-0.4439</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.422</v>
+        <v>-0.8497</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.141</v>
+        <v>-0.1524</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0272</v>
+        <v>0.2519</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1138</v>
+        <v>-0.4044</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2988</v>
+        <v>-1.2592</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5228</v>
+        <v>-0.602</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2241</v>
+        <v>-0.6573</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-1.7094</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9363</v>
+        <v>-0.1332</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6596</v>
+        <v>-1.5762</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0771</v>
+        <v>-0.3692</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7897999999999999</v>
+        <v>-0.215</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7127</v>
+        <v>-0.1543</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8004</v>
+        <v>-1.3401</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1465</v>
+        <v>0.0818</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9469</v>
+        <v>-1.422</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
         <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0482</v>
+        <v>-0.1582</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7196</v>
+        <v>-0.1452</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3286</v>
+        <v>-0.013</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6388</v>
+        <v>-1.7198</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6907</v>
+        <v>-1.8767</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9481000000000001</v>
+        <v>0.1568</v>
       </c>
       <c r="G18" t="n">
-        <v>1.597</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2185</v>
+        <v>0.9363</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3785</v>
+        <v>-1.6596</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8905</v>
+        <v>0.0771</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6624</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>2.2281</v>
+        <v>-0.7127</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2936</v>
+        <v>-0.8004</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4439</v>
+        <v>0.1465</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8497</v>
+        <v>-0.9469</v>
       </c>
       <c r="P18" t="n">
         <v>-1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5399</v>
+        <v>0.6271</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1019</v>
+        <v>0.3657</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.438</v>
+        <v>0.2614</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0179</v>
+        <v>-2.0185</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4469</v>
+        <v>-1.6828</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.571</v>
+        <v>-0.3357</v>
       </c>
       <c r="G19" t="n">
         <v>-1.9121</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2166</v>
+        <v>-0.2172</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4955</v>
+        <v>0.2596</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7121</v>
+        <v>-0.4769</v>
       </c>
       <c r="V19" t="n">
         <v>0.1107</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.228</v>
+        <v>-2.9585</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6787</v>
+        <v>-1.4428</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5494</v>
+        <v>-1.5158</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7765</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4336</v>
+        <v>-0.1641</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5149</v>
+        <v>-0.279</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0813</v>
+        <v>0.1149</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3943</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7254</v>
+        <v>-3.0471</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6852</v>
+        <v>-1.8874</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0402</v>
+        <v>-1.1597</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.7317</v>
+        <v>0.2218</v>
       </c>
       <c r="H21" t="n">
-        <v>0.143</v>
+        <v>-0.695</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.8747</v>
+        <v>0.9169</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4339</v>
+        <v>1.4619</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3865</v>
+        <v>-0.0939</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8204</v>
+        <v>1.5557</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2978</v>
+        <v>-1.24</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2435</v>
+        <v>-0.6012</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0543</v>
+        <v>-0.6389</v>
       </c>
       <c r="P21" t="n">
-        <v>0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8465</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9085</v>
+        <v>0.13</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0619</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2932</v>
+        <v>-4.3488</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.831</v>
+        <v>-2.2749</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4622</v>
+        <v>-2.0738</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2218</v>
+        <v>-3.7317</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.695</v>
+        <v>0.143</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9169</v>
+        <v>-3.8747</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4619</v>
+        <v>-1.4339</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0939</v>
+        <v>0.3865</v>
       </c>
       <c r="L22" t="n">
-        <v>1.5557</v>
+        <v>-1.8204</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.24</v>
+        <v>-2.2978</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6012</v>
+        <v>-0.2435</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6389</v>
+        <v>-2.0543</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8191</v>
+        <v>0.2232</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8136</v>
+        <v>0.3187</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0055</v>
+        <v>-0.0955</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-13.786</v>
+        <v>-13.7859</v>
       </c>
       <c r="E23" t="n">
         <v>-3.5972</v>
@@ -2215,7 +2215,7 @@
         <v>-4.5747</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1076999999999996</v>
+        <v>-0.1076999999999998</v>
       </c>
       <c r="I23" t="n">
         <v>-4.466699999999999</v>
@@ -2239,7 +2239,7 @@
         <v>-11.8769</v>
       </c>
       <c r="P23" t="n">
-        <v>-6.9587</v>
+        <v>-6.958699999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-19.7161</v>
@@ -2248,13 +2248,13 @@
         <v>12.7575</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7863999999999998</v>
+        <v>-0.7863</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2213</v>
+        <v>1.2211</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.0075</v>
+        <v>-2.0076</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4665</v>
